--- a/InputData/elec/MPCbS/Max Potential Capacity by Source.xlsx
+++ b/InputData/elec/MPCbS/Max Potential Capacity by Source.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11027"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/Postdoc Projects/eps-indonesia-cpl/InputData/elec/MPCbS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C3AB194-208F-D940-9703-BD13AABA1173}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC11F070-45E2-CB41-BBFF-686B3D5B43A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="Data" sheetId="2" r:id="rId2"/>
-    <sheet name="MPCbS" sheetId="3" r:id="rId3"/>
+    <sheet name="Data-Renewables" sheetId="4" r:id="rId3"/>
+    <sheet name="MPCbS" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="53">
   <si>
     <t>MPCbS Max Potential Capacity by Source</t>
   </si>
@@ -149,6 +150,54 @@
   </si>
   <si>
     <t>US MPCCS</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Maximum Potential Capacity (MW)</t>
+  </si>
+  <si>
+    <t>Maximum Potential Capacity (GW)</t>
+  </si>
+  <si>
+    <t>Tito Wijayanto , Dzikri Firmansyah Hakam * , Prodia Nur Kemala</t>
+  </si>
+  <si>
+    <t>Vision for Indonesia’s 2050 power generation: Scenarios of hydrogen integration, nuclear energy prospects, and coal phase-out impact</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.sftr.2025.100438</t>
+  </si>
+  <si>
+    <t>GW to MW</t>
+  </si>
+  <si>
+    <t>The Future of Wind Power Plants in Indonesia: Potential, Challenges, and Policies</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.3390/su17031312</t>
+  </si>
+  <si>
+    <t>Looking forward to Indonesia's solar future</t>
+  </si>
+  <si>
+    <t>ANTARA 2024</t>
+  </si>
+  <si>
+    <t>Nugroho Agung Pambud et al.</t>
+  </si>
+  <si>
+    <t>https://en.antaranews.com/news/323823/looking-forward-to-indonesias-solar-future#:~:text=The%20country's%20solar%20potential%20alone%20stands%20at,GW%2C%2024%20GW%2C%20and%2020%20GW%20respectively.&amp;text=While%20the%20potential%20for%20solar%20energy%20is,GW%2C%20its%20realization%20reached%20just%20573%20MW.</t>
+  </si>
+  <si>
+    <t>Beyond 207 Gigawatts: Unleashing Indonesia’s Solar Potential</t>
+  </si>
+  <si>
+    <t>IESR</t>
+  </si>
+  <si>
+    <t>https://iesr.or.id/en/pustaka/beyond-207-gigawatts-unleashing-indonesias-solar-potential/#:~:text=A%20geospatial%20assessment%20of%20Indonesia's,land%2Duse%20exclusions%20scenarios).</t>
   </si>
 </sst>
 </file>
@@ -194,18 +243,17 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="10"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
+      <scheme val="major"/>
     </font>
   </fonts>
   <fills count="4">
@@ -244,10 +292,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -259,15 +308,19 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="11" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -530,7 +583,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B1000"/>
+  <dimension ref="A1:B1010"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.6640625" customWidth="1"/>
@@ -571,73 +624,141 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B10" s="7"/>
+    <row r="9" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="5">
+        <v>2025</v>
+      </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B12" s="4"/>
+      <c r="B12" s="12" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B14" s="8"/>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B17" s="7"/>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B14" s="7"/>
+    </row>
+    <row r="15" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="14" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="13" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B17" s="11">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B18" s="12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B19" s="4"/>
     </row>
-    <row r="21" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="9"/>
-    </row>
-    <row r="22" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="23" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="10"/>
-    </row>
-    <row r="24" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="25" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="1" t="s">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B20" s="4"/>
+    </row>
+    <row r="21" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B22" s="13" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B23" s="4">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B24" s="12" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="26" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="27" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B27" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B28" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B29" s="5">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B30" s="12" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B31" s="3"/>
+    </row>
+    <row r="32" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B32" s="3"/>
+    </row>
+    <row r="33" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B33" s="3"/>
+    </row>
+    <row r="34" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="35" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="3" t="s">
+    <row r="36" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="3" t="s">
+    <row r="37" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="3" t="s">
+    <row r="38" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="3" t="s">
+    <row r="39" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="31" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="40" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="41" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="42" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="43" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="44" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="45" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="46" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="47" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="48" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -1590,9 +1711,23 @@
     <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1002" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1003" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1004" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1005" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1006" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1007" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1008" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1009" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1010" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B7" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="B12" r:id="rId2" tooltip="Persistent link using digital object identifier" xr:uid="{344CCEC0-B72D-DA4C-87D5-C0D7B75EA4FE}"/>
+    <hyperlink ref="B18" r:id="rId3" xr:uid="{86A0A910-AD48-094A-9EE4-43392EFD89A4}"/>
+    <hyperlink ref="B24" r:id="rId4" location=":~:text=The%20country's%20solar%20potential%20alone%20stands%20at,GW%2C%2024%20GW%2C%20and%2020%20GW%20respectively.&amp;text=While%20the%20potential%20for%20solar%20energy%20is,GW%2C%20its%20realization%20reached%20just%20573%20MW." display="https://en.antaranews.com/news/323823/looking-forward-to-indonesias-solar-future#:~:text=The%20country's%20solar%20potential%20alone%20stands%20at,GW%2C%2024%20GW%2C%20and%2020%20GW%20respectively.&amp;text=While%20the%20potential%20for%20solar%20energy%20is,GW%2C%20its%20realization%20reached%20just%20573%20MW." xr:uid="{DA9AC5AE-E318-9D40-984B-37342CF78D6F}"/>
+    <hyperlink ref="B30" r:id="rId5" location=":~:text=A%20geospatial%20assessment%20of%20Indonesia's,land%2Duse%20exclusions%20scenarios)." xr:uid="{2FBA03EF-D4EF-9840-B775-F7619F903A37}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="portrait"/>
@@ -1631,10 +1766,10 @@
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="11">
+      <c r="B3" s="8">
         <f>6.3*1000</f>
         <v>6300</v>
       </c>
@@ -1646,10 +1781,10 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="11">
+      <c r="B4" s="8">
         <f>25*1000</f>
         <v>25000</v>
       </c>
@@ -1661,10 +1796,10 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="11">
+      <c r="B5" s="8">
         <f>6473.3*1000</f>
         <v>6473300</v>
       </c>
@@ -1676,10 +1811,10 @@
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="8" t="s">
         <v>17</v>
       </c>
       <c r="G6" s="3" t="s">
@@ -1690,10 +1825,10 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="11">
+      <c r="B7" s="8">
         <f>30.73*1000</f>
         <v>30730</v>
       </c>
@@ -1705,10 +1840,10 @@
       </c>
     </row>
     <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="8" t="s">
         <v>17</v>
       </c>
       <c r="G8" s="3" t="s">
@@ -1719,16 +1854,16 @@
       </c>
     </row>
     <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="8" t="s">
         <v>17</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H9" s="3">
+      <c r="H9" s="10">
         <v>38000000</v>
       </c>
     </row>
@@ -1759,7 +1894,7 @@
         <v>30</v>
       </c>
       <c r="H12" s="3">
-        <v>9000000000000</v>
+        <v>153000</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1818,7 +1953,7 @@
       <c r="A18" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="12">
+      <c r="B18" s="9">
         <f>H3</f>
         <v>9000000000000</v>
       </c>
@@ -1833,7 +1968,7 @@
       <c r="A19" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="12">
+      <c r="B19" s="9">
         <f t="shared" ref="B19:B20" si="0">H4</f>
         <v>9000000000000</v>
       </c>
@@ -1842,7 +1977,7 @@
       <c r="A20" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="12">
+      <c r="B20" s="9">
         <f t="shared" si="0"/>
         <v>9000000000000</v>
       </c>
@@ -1851,7 +1986,7 @@
       <c r="A21" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B21" s="13">
+      <c r="B21" s="10">
         <f>75091+19385</f>
         <v>94476</v>
       </c>
@@ -1860,7 +1995,7 @@
       <c r="A22" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B22" s="13">
+      <c r="B22" s="10">
         <v>60647</v>
       </c>
     </row>
@@ -1868,7 +2003,7 @@
       <c r="A23" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B23" s="13">
+      <c r="B23" s="10">
         <v>207896</v>
       </c>
     </row>
@@ -1876,7 +2011,7 @@
       <c r="A24" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B24" s="13">
+      <c r="B24" s="10">
         <f>H9</f>
         <v>38000000</v>
       </c>
@@ -1885,7 +2020,7 @@
       <c r="A25" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B25" s="13">
+      <c r="B25" s="10">
         <v>32654</v>
       </c>
     </row>
@@ -1893,7 +2028,7 @@
       <c r="A26" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B26" s="13">
+      <c r="B26" s="10">
         <v>29544</v>
       </c>
     </row>
@@ -1901,16 +2036,16 @@
       <c r="A27" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B27" s="12">
+      <c r="B27" s="9">
         <f>H12</f>
-        <v>9000000000000</v>
+        <v>153000</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B28" s="12">
+      <c r="B28" s="9">
         <f t="shared" ref="B28:B33" si="1">H13</f>
         <v>9000000000000</v>
       </c>
@@ -1919,7 +2054,7 @@
       <c r="A29" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B29" s="12">
+      <c r="B29" s="9">
         <f t="shared" si="1"/>
         <v>9000000000000</v>
       </c>
@@ -1928,7 +2063,7 @@
       <c r="A30" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B30" s="12">
+      <c r="B30" s="9">
         <f t="shared" si="1"/>
         <v>4200000</v>
       </c>
@@ -1937,7 +2072,7 @@
       <c r="A31" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B31" s="12">
+      <c r="B31" s="9">
         <f t="shared" si="1"/>
         <v>9000000000000</v>
       </c>
@@ -1946,7 +2081,7 @@
       <c r="A32" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B32" s="12">
+      <c r="B32" s="9">
         <f t="shared" si="1"/>
         <v>9000000000000</v>
       </c>
@@ -1955,7 +2090,7 @@
       <c r="A33" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B33" s="12">
+      <c r="B33" s="9">
         <f t="shared" si="1"/>
         <v>8031</v>
       </c>
@@ -2921,6 +3056,132 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27209D21-DE46-9B49-910B-40254B76F16A}">
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2">
+        <v>95</v>
+      </c>
+      <c r="C2" s="9">
+        <f>B2*$B$11</f>
+        <v>95000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3">
+        <v>60.6</v>
+      </c>
+      <c r="C3" s="9">
+        <f t="shared" ref="C3:C9" si="0">B3*$B$11</f>
+        <v>60600</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4">
+        <v>19835</v>
+      </c>
+      <c r="C4" s="9">
+        <f t="shared" si="0"/>
+        <v>19835000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5">
+        <f>B4</f>
+        <v>19835</v>
+      </c>
+      <c r="C5" s="9">
+        <f t="shared" si="0"/>
+        <v>19835000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6">
+        <v>32.6</v>
+      </c>
+      <c r="C6" s="9">
+        <f t="shared" si="0"/>
+        <v>32600</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7">
+        <v>28.5</v>
+      </c>
+      <c r="C7" s="9">
+        <f t="shared" si="0"/>
+        <v>28500</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8">
+        <v>94.2</v>
+      </c>
+      <c r="C8" s="9">
+        <f t="shared" si="0"/>
+        <v>94200</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9">
+        <v>32.6</v>
+      </c>
+      <c r="C9" s="9">
+        <f t="shared" si="0"/>
+        <v>32600</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11">
+        <v>1000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor rgb="FF1F497D"/>
@@ -2945,997 +3206,997 @@
       <c r="A2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="9">
         <f>Data!B18</f>
         <v>9000000000000</v>
       </c>
-      <c r="C2" s="12"/>
+      <c r="C2" s="9"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="12">
+      <c r="B3" s="9">
         <f>Data!B19</f>
         <v>9000000000000</v>
       </c>
-      <c r="C3" s="12"/>
+      <c r="C3" s="9"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="12">
+      <c r="B4" s="9">
         <f>Data!B20</f>
         <v>9000000000000</v>
       </c>
-      <c r="C4" s="12"/>
+      <c r="C4" s="9"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="12">
-        <f>Data!B21</f>
-        <v>94476</v>
-      </c>
-      <c r="C5" s="12"/>
+      <c r="B5" s="9">
+        <f>'Data-Renewables'!C2</f>
+        <v>95000</v>
+      </c>
+      <c r="C5" s="9"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="12">
-        <f>Data!B22</f>
-        <v>60647</v>
-      </c>
-      <c r="C6" s="12"/>
+      <c r="B6" s="9">
+        <f>'Data-Renewables'!C3</f>
+        <v>60600</v>
+      </c>
+      <c r="C6" s="9"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="12">
-        <f>Data!B23</f>
-        <v>207896</v>
-      </c>
-      <c r="C7" s="12"/>
+      <c r="B7" s="9">
+        <f>'Data-Renewables'!C4</f>
+        <v>19835000</v>
+      </c>
+      <c r="C7" s="9"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="12">
-        <f>Data!B24</f>
-        <v>38000000</v>
-      </c>
-      <c r="C8" s="12"/>
+      <c r="B8" s="9">
+        <f>'Data-Renewables'!C5</f>
+        <v>19835000</v>
+      </c>
+      <c r="C8" s="9"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="12">
-        <f>Data!B25</f>
-        <v>32654</v>
-      </c>
-      <c r="C9" s="12"/>
+      <c r="B9" s="9">
+        <f>'Data-Renewables'!C6</f>
+        <v>32600</v>
+      </c>
+      <c r="C9" s="9"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="12">
-        <f>Data!B26</f>
-        <v>29544</v>
-      </c>
-      <c r="C10" s="12"/>
+      <c r="B10" s="9">
+        <f>'Data-Renewables'!C7</f>
+        <v>28500</v>
+      </c>
+      <c r="C10" s="9"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="9">
         <f>Data!B27</f>
-        <v>9000000000000</v>
-      </c>
-      <c r="C11" s="12"/>
+        <v>153000</v>
+      </c>
+      <c r="C11" s="9"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="12">
+      <c r="B12" s="9">
         <f>Data!B28</f>
         <v>9000000000000</v>
       </c>
-      <c r="C12" s="12"/>
+      <c r="C12" s="9"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B13" s="12">
+      <c r="B13" s="9">
         <f>Data!B29</f>
         <v>9000000000000</v>
       </c>
-      <c r="C13" s="12"/>
+      <c r="C13" s="9"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B14" s="12">
-        <f>Data!B30</f>
-        <v>4200000</v>
-      </c>
-      <c r="C14" s="12"/>
+      <c r="B14" s="9">
+        <f>'Data-Renewables'!C8</f>
+        <v>94200</v>
+      </c>
+      <c r="C14" s="9"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B15" s="12">
-        <f>Data!B31</f>
-        <v>9000000000000</v>
-      </c>
-      <c r="C15" s="12"/>
+      <c r="B15" s="9">
+        <f>B11</f>
+        <v>153000</v>
+      </c>
+      <c r="C15" s="9"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B16" s="12">
-        <f>Data!B32</f>
-        <v>9000000000000</v>
-      </c>
-      <c r="C16" s="12"/>
+      <c r="B16" s="9">
+        <f>B11</f>
+        <v>153000</v>
+      </c>
+      <c r="C16" s="9"/>
     </row>
     <row r="17" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B17" s="12">
-        <f>Data!B33</f>
-        <v>8031</v>
-      </c>
-      <c r="C17" s="12"/>
+      <c r="B17" s="9">
+        <f>'Data-Renewables'!C9</f>
+        <v>32600</v>
+      </c>
+      <c r="C17" s="9"/>
     </row>
     <row r="21" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="22" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="23" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="24" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="25" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="12"/>
-      <c r="C25" s="12"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="12"/>
-      <c r="H25" s="12"/>
-      <c r="I25" s="12"/>
-      <c r="J25" s="12"/>
-      <c r="K25" s="12"/>
-      <c r="L25" s="12"/>
-      <c r="M25" s="12"/>
-      <c r="N25" s="12"/>
-      <c r="O25" s="12"/>
-      <c r="P25" s="12"/>
-      <c r="Q25" s="12"/>
-      <c r="R25" s="12"/>
-      <c r="S25" s="12"/>
-      <c r="T25" s="12"/>
-      <c r="U25" s="12"/>
-      <c r="V25" s="12"/>
-      <c r="W25" s="12"/>
-      <c r="X25" s="12"/>
-      <c r="Y25" s="12"/>
-      <c r="Z25" s="12"/>
-      <c r="AA25" s="12"/>
-      <c r="AB25" s="12"/>
-      <c r="AC25" s="12"/>
-      <c r="AD25" s="12"/>
-      <c r="AE25" s="12"/>
-      <c r="AF25" s="12"/>
-      <c r="AG25" s="12"/>
-      <c r="AH25" s="12"/>
-      <c r="AI25" s="12"/>
-      <c r="AJ25" s="12"/>
-      <c r="AK25" s="12"/>
-      <c r="AL25" s="12"/>
-      <c r="AM25" s="12"/>
-      <c r="AN25" s="12"/>
-      <c r="AO25" s="12"/>
-      <c r="AP25" s="12"/>
-      <c r="AQ25" s="12"/>
-      <c r="AR25" s="12"/>
-      <c r="AS25" s="12"/>
-      <c r="AT25" s="12"/>
-      <c r="AU25" s="12"/>
-      <c r="AV25" s="12"/>
-      <c r="AW25" s="12"/>
-      <c r="AX25" s="12"/>
-      <c r="AY25" s="12"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="9"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="9"/>
+      <c r="K25" s="9"/>
+      <c r="L25" s="9"/>
+      <c r="M25" s="9"/>
+      <c r="N25" s="9"/>
+      <c r="O25" s="9"/>
+      <c r="P25" s="9"/>
+      <c r="Q25" s="9"/>
+      <c r="R25" s="9"/>
+      <c r="S25" s="9"/>
+      <c r="T25" s="9"/>
+      <c r="U25" s="9"/>
+      <c r="V25" s="9"/>
+      <c r="W25" s="9"/>
+      <c r="X25" s="9"/>
+      <c r="Y25" s="9"/>
+      <c r="Z25" s="9"/>
+      <c r="AA25" s="9"/>
+      <c r="AB25" s="9"/>
+      <c r="AC25" s="9"/>
+      <c r="AD25" s="9"/>
+      <c r="AE25" s="9"/>
+      <c r="AF25" s="9"/>
+      <c r="AG25" s="9"/>
+      <c r="AH25" s="9"/>
+      <c r="AI25" s="9"/>
+      <c r="AJ25" s="9"/>
+      <c r="AK25" s="9"/>
+      <c r="AL25" s="9"/>
+      <c r="AM25" s="9"/>
+      <c r="AN25" s="9"/>
+      <c r="AO25" s="9"/>
+      <c r="AP25" s="9"/>
+      <c r="AQ25" s="9"/>
+      <c r="AR25" s="9"/>
+      <c r="AS25" s="9"/>
+      <c r="AT25" s="9"/>
+      <c r="AU25" s="9"/>
+      <c r="AV25" s="9"/>
+      <c r="AW25" s="9"/>
+      <c r="AX25" s="9"/>
+      <c r="AY25" s="9"/>
     </row>
     <row r="26" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="12"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="12"/>
-      <c r="H26" s="12"/>
-      <c r="I26" s="12"/>
-      <c r="J26" s="12"/>
-      <c r="K26" s="12"/>
-      <c r="L26" s="12"/>
-      <c r="M26" s="12"/>
-      <c r="N26" s="12"/>
-      <c r="O26" s="12"/>
-      <c r="P26" s="12"/>
-      <c r="Q26" s="12"/>
-      <c r="R26" s="12"/>
-      <c r="S26" s="12"/>
-      <c r="T26" s="12"/>
-      <c r="U26" s="12"/>
-      <c r="V26" s="12"/>
-      <c r="W26" s="12"/>
-      <c r="X26" s="12"/>
-      <c r="Y26" s="12"/>
-      <c r="Z26" s="12"/>
-      <c r="AA26" s="12"/>
-      <c r="AB26" s="12"/>
-      <c r="AC26" s="12"/>
-      <c r="AD26" s="12"/>
-      <c r="AE26" s="12"/>
-      <c r="AF26" s="12"/>
-      <c r="AG26" s="12"/>
-      <c r="AH26" s="12"/>
-      <c r="AI26" s="12"/>
-      <c r="AJ26" s="12"/>
-      <c r="AK26" s="12"/>
-      <c r="AL26" s="12"/>
-      <c r="AM26" s="12"/>
-      <c r="AN26" s="12"/>
-      <c r="AO26" s="12"/>
-      <c r="AP26" s="12"/>
-      <c r="AQ26" s="12"/>
-      <c r="AR26" s="12"/>
-      <c r="AS26" s="12"/>
-      <c r="AT26" s="12"/>
-      <c r="AU26" s="12"/>
-      <c r="AV26" s="12"/>
-      <c r="AW26" s="12"/>
-      <c r="AX26" s="12"/>
-      <c r="AY26" s="12"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="9"/>
+      <c r="I26" s="9"/>
+      <c r="J26" s="9"/>
+      <c r="K26" s="9"/>
+      <c r="L26" s="9"/>
+      <c r="M26" s="9"/>
+      <c r="N26" s="9"/>
+      <c r="O26" s="9"/>
+      <c r="P26" s="9"/>
+      <c r="Q26" s="9"/>
+      <c r="R26" s="9"/>
+      <c r="S26" s="9"/>
+      <c r="T26" s="9"/>
+      <c r="U26" s="9"/>
+      <c r="V26" s="9"/>
+      <c r="W26" s="9"/>
+      <c r="X26" s="9"/>
+      <c r="Y26" s="9"/>
+      <c r="Z26" s="9"/>
+      <c r="AA26" s="9"/>
+      <c r="AB26" s="9"/>
+      <c r="AC26" s="9"/>
+      <c r="AD26" s="9"/>
+      <c r="AE26" s="9"/>
+      <c r="AF26" s="9"/>
+      <c r="AG26" s="9"/>
+      <c r="AH26" s="9"/>
+      <c r="AI26" s="9"/>
+      <c r="AJ26" s="9"/>
+      <c r="AK26" s="9"/>
+      <c r="AL26" s="9"/>
+      <c r="AM26" s="9"/>
+      <c r="AN26" s="9"/>
+      <c r="AO26" s="9"/>
+      <c r="AP26" s="9"/>
+      <c r="AQ26" s="9"/>
+      <c r="AR26" s="9"/>
+      <c r="AS26" s="9"/>
+      <c r="AT26" s="9"/>
+      <c r="AU26" s="9"/>
+      <c r="AV26" s="9"/>
+      <c r="AW26" s="9"/>
+      <c r="AX26" s="9"/>
+      <c r="AY26" s="9"/>
     </row>
     <row r="27" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="12"/>
-      <c r="C27" s="12"/>
-      <c r="D27" s="12"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="12"/>
-      <c r="H27" s="12"/>
-      <c r="I27" s="12"/>
-      <c r="J27" s="12"/>
-      <c r="K27" s="12"/>
-      <c r="L27" s="12"/>
-      <c r="M27" s="12"/>
-      <c r="N27" s="12"/>
-      <c r="O27" s="12"/>
-      <c r="P27" s="12"/>
-      <c r="Q27" s="12"/>
-      <c r="R27" s="12"/>
-      <c r="S27" s="12"/>
-      <c r="T27" s="12"/>
-      <c r="U27" s="12"/>
-      <c r="V27" s="12"/>
-      <c r="W27" s="12"/>
-      <c r="X27" s="12"/>
-      <c r="Y27" s="12"/>
-      <c r="Z27" s="12"/>
-      <c r="AA27" s="12"/>
-      <c r="AB27" s="12"/>
-      <c r="AC27" s="12"/>
-      <c r="AD27" s="12"/>
-      <c r="AE27" s="12"/>
-      <c r="AF27" s="12"/>
-      <c r="AG27" s="12"/>
-      <c r="AH27" s="12"/>
-      <c r="AI27" s="12"/>
-      <c r="AJ27" s="12"/>
-      <c r="AK27" s="12"/>
-      <c r="AL27" s="12"/>
-      <c r="AM27" s="12"/>
-      <c r="AN27" s="12"/>
-      <c r="AO27" s="12"/>
-      <c r="AP27" s="12"/>
-      <c r="AQ27" s="12"/>
-      <c r="AR27" s="12"/>
-      <c r="AS27" s="12"/>
-      <c r="AT27" s="12"/>
-      <c r="AU27" s="12"/>
-      <c r="AV27" s="12"/>
-      <c r="AW27" s="12"/>
-      <c r="AX27" s="12"/>
-      <c r="AY27" s="12"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="9"/>
+      <c r="I27" s="9"/>
+      <c r="J27" s="9"/>
+      <c r="K27" s="9"/>
+      <c r="L27" s="9"/>
+      <c r="M27" s="9"/>
+      <c r="N27" s="9"/>
+      <c r="O27" s="9"/>
+      <c r="P27" s="9"/>
+      <c r="Q27" s="9"/>
+      <c r="R27" s="9"/>
+      <c r="S27" s="9"/>
+      <c r="T27" s="9"/>
+      <c r="U27" s="9"/>
+      <c r="V27" s="9"/>
+      <c r="W27" s="9"/>
+      <c r="X27" s="9"/>
+      <c r="Y27" s="9"/>
+      <c r="Z27" s="9"/>
+      <c r="AA27" s="9"/>
+      <c r="AB27" s="9"/>
+      <c r="AC27" s="9"/>
+      <c r="AD27" s="9"/>
+      <c r="AE27" s="9"/>
+      <c r="AF27" s="9"/>
+      <c r="AG27" s="9"/>
+      <c r="AH27" s="9"/>
+      <c r="AI27" s="9"/>
+      <c r="AJ27" s="9"/>
+      <c r="AK27" s="9"/>
+      <c r="AL27" s="9"/>
+      <c r="AM27" s="9"/>
+      <c r="AN27" s="9"/>
+      <c r="AO27" s="9"/>
+      <c r="AP27" s="9"/>
+      <c r="AQ27" s="9"/>
+      <c r="AR27" s="9"/>
+      <c r="AS27" s="9"/>
+      <c r="AT27" s="9"/>
+      <c r="AU27" s="9"/>
+      <c r="AV27" s="9"/>
+      <c r="AW27" s="9"/>
+      <c r="AX27" s="9"/>
+      <c r="AY27" s="9"/>
     </row>
     <row r="28" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="12"/>
-      <c r="C28" s="12"/>
-      <c r="D28" s="12"/>
-      <c r="E28" s="12"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="12"/>
-      <c r="H28" s="12"/>
-      <c r="I28" s="12"/>
-      <c r="J28" s="12"/>
-      <c r="K28" s="12"/>
-      <c r="L28" s="12"/>
-      <c r="M28" s="12"/>
-      <c r="N28" s="12"/>
-      <c r="O28" s="12"/>
-      <c r="P28" s="12"/>
-      <c r="Q28" s="12"/>
-      <c r="R28" s="12"/>
-      <c r="S28" s="12"/>
-      <c r="T28" s="12"/>
-      <c r="U28" s="12"/>
-      <c r="V28" s="12"/>
-      <c r="W28" s="12"/>
-      <c r="X28" s="12"/>
-      <c r="Y28" s="12"/>
-      <c r="Z28" s="12"/>
-      <c r="AA28" s="12"/>
-      <c r="AB28" s="12"/>
-      <c r="AC28" s="12"/>
-      <c r="AD28" s="12"/>
-      <c r="AE28" s="12"/>
-      <c r="AF28" s="12"/>
-      <c r="AG28" s="12"/>
-      <c r="AH28" s="12"/>
-      <c r="AI28" s="12"/>
-      <c r="AJ28" s="12"/>
-      <c r="AK28" s="12"/>
-      <c r="AL28" s="12"/>
-      <c r="AM28" s="12"/>
-      <c r="AN28" s="12"/>
-      <c r="AO28" s="12"/>
-      <c r="AP28" s="12"/>
-      <c r="AQ28" s="12"/>
-      <c r="AR28" s="12"/>
-      <c r="AS28" s="12"/>
-      <c r="AT28" s="12"/>
-      <c r="AU28" s="12"/>
-      <c r="AV28" s="12"/>
-      <c r="AW28" s="12"/>
-      <c r="AX28" s="12"/>
-      <c r="AY28" s="12"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="9"/>
+      <c r="I28" s="9"/>
+      <c r="J28" s="9"/>
+      <c r="K28" s="9"/>
+      <c r="L28" s="9"/>
+      <c r="M28" s="9"/>
+      <c r="N28" s="9"/>
+      <c r="O28" s="9"/>
+      <c r="P28" s="9"/>
+      <c r="Q28" s="9"/>
+      <c r="R28" s="9"/>
+      <c r="S28" s="9"/>
+      <c r="T28" s="9"/>
+      <c r="U28" s="9"/>
+      <c r="V28" s="9"/>
+      <c r="W28" s="9"/>
+      <c r="X28" s="9"/>
+      <c r="Y28" s="9"/>
+      <c r="Z28" s="9"/>
+      <c r="AA28" s="9"/>
+      <c r="AB28" s="9"/>
+      <c r="AC28" s="9"/>
+      <c r="AD28" s="9"/>
+      <c r="AE28" s="9"/>
+      <c r="AF28" s="9"/>
+      <c r="AG28" s="9"/>
+      <c r="AH28" s="9"/>
+      <c r="AI28" s="9"/>
+      <c r="AJ28" s="9"/>
+      <c r="AK28" s="9"/>
+      <c r="AL28" s="9"/>
+      <c r="AM28" s="9"/>
+      <c r="AN28" s="9"/>
+      <c r="AO28" s="9"/>
+      <c r="AP28" s="9"/>
+      <c r="AQ28" s="9"/>
+      <c r="AR28" s="9"/>
+      <c r="AS28" s="9"/>
+      <c r="AT28" s="9"/>
+      <c r="AU28" s="9"/>
+      <c r="AV28" s="9"/>
+      <c r="AW28" s="9"/>
+      <c r="AX28" s="9"/>
+      <c r="AY28" s="9"/>
     </row>
     <row r="29" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="12"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="12"/>
-      <c r="H29" s="12"/>
-      <c r="I29" s="12"/>
-      <c r="J29" s="12"/>
-      <c r="K29" s="12"/>
-      <c r="L29" s="12"/>
-      <c r="M29" s="12"/>
-      <c r="N29" s="12"/>
-      <c r="O29" s="12"/>
-      <c r="P29" s="12"/>
-      <c r="Q29" s="12"/>
-      <c r="R29" s="12"/>
-      <c r="S29" s="12"/>
-      <c r="T29" s="12"/>
-      <c r="U29" s="12"/>
-      <c r="V29" s="12"/>
-      <c r="W29" s="12"/>
-      <c r="X29" s="12"/>
-      <c r="Y29" s="12"/>
-      <c r="Z29" s="12"/>
-      <c r="AA29" s="12"/>
-      <c r="AB29" s="12"/>
-      <c r="AC29" s="12"/>
-      <c r="AD29" s="12"/>
-      <c r="AE29" s="12"/>
-      <c r="AF29" s="12"/>
-      <c r="AG29" s="12"/>
-      <c r="AH29" s="12"/>
-      <c r="AI29" s="12"/>
-      <c r="AJ29" s="12"/>
-      <c r="AK29" s="12"/>
-      <c r="AL29" s="12"/>
-      <c r="AM29" s="12"/>
-      <c r="AN29" s="12"/>
-      <c r="AO29" s="12"/>
-      <c r="AP29" s="12"/>
-      <c r="AQ29" s="12"/>
-      <c r="AR29" s="12"/>
-      <c r="AS29" s="12"/>
-      <c r="AT29" s="12"/>
-      <c r="AU29" s="12"/>
-      <c r="AV29" s="12"/>
-      <c r="AW29" s="12"/>
-      <c r="AX29" s="12"/>
-      <c r="AY29" s="12"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="9"/>
+      <c r="I29" s="9"/>
+      <c r="J29" s="9"/>
+      <c r="K29" s="9"/>
+      <c r="L29" s="9"/>
+      <c r="M29" s="9"/>
+      <c r="N29" s="9"/>
+      <c r="O29" s="9"/>
+      <c r="P29" s="9"/>
+      <c r="Q29" s="9"/>
+      <c r="R29" s="9"/>
+      <c r="S29" s="9"/>
+      <c r="T29" s="9"/>
+      <c r="U29" s="9"/>
+      <c r="V29" s="9"/>
+      <c r="W29" s="9"/>
+      <c r="X29" s="9"/>
+      <c r="Y29" s="9"/>
+      <c r="Z29" s="9"/>
+      <c r="AA29" s="9"/>
+      <c r="AB29" s="9"/>
+      <c r="AC29" s="9"/>
+      <c r="AD29" s="9"/>
+      <c r="AE29" s="9"/>
+      <c r="AF29" s="9"/>
+      <c r="AG29" s="9"/>
+      <c r="AH29" s="9"/>
+      <c r="AI29" s="9"/>
+      <c r="AJ29" s="9"/>
+      <c r="AK29" s="9"/>
+      <c r="AL29" s="9"/>
+      <c r="AM29" s="9"/>
+      <c r="AN29" s="9"/>
+      <c r="AO29" s="9"/>
+      <c r="AP29" s="9"/>
+      <c r="AQ29" s="9"/>
+      <c r="AR29" s="9"/>
+      <c r="AS29" s="9"/>
+      <c r="AT29" s="9"/>
+      <c r="AU29" s="9"/>
+      <c r="AV29" s="9"/>
+      <c r="AW29" s="9"/>
+      <c r="AX29" s="9"/>
+      <c r="AY29" s="9"/>
     </row>
     <row r="30" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="12"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="12"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="12"/>
-      <c r="H30" s="12"/>
-      <c r="I30" s="12"/>
-      <c r="J30" s="12"/>
-      <c r="K30" s="12"/>
-      <c r="L30" s="12"/>
-      <c r="M30" s="12"/>
-      <c r="N30" s="12"/>
-      <c r="O30" s="12"/>
-      <c r="P30" s="12"/>
-      <c r="Q30" s="12"/>
-      <c r="R30" s="12"/>
-      <c r="S30" s="12"/>
-      <c r="T30" s="12"/>
-      <c r="U30" s="12"/>
-      <c r="V30" s="12"/>
-      <c r="W30" s="12"/>
-      <c r="X30" s="12"/>
-      <c r="Y30" s="12"/>
-      <c r="Z30" s="12"/>
-      <c r="AA30" s="12"/>
-      <c r="AB30" s="12"/>
-      <c r="AC30" s="12"/>
-      <c r="AD30" s="12"/>
-      <c r="AE30" s="12"/>
-      <c r="AF30" s="12"/>
-      <c r="AG30" s="12"/>
-      <c r="AH30" s="12"/>
-      <c r="AI30" s="12"/>
-      <c r="AJ30" s="12"/>
-      <c r="AK30" s="12"/>
-      <c r="AL30" s="12"/>
-      <c r="AM30" s="12"/>
-      <c r="AN30" s="12"/>
-      <c r="AO30" s="12"/>
-      <c r="AP30" s="12"/>
-      <c r="AQ30" s="12"/>
-      <c r="AR30" s="12"/>
-      <c r="AS30" s="12"/>
-      <c r="AT30" s="12"/>
-      <c r="AU30" s="12"/>
-      <c r="AV30" s="12"/>
-      <c r="AW30" s="12"/>
-      <c r="AX30" s="12"/>
-      <c r="AY30" s="12"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="9"/>
+      <c r="I30" s="9"/>
+      <c r="J30" s="9"/>
+      <c r="K30" s="9"/>
+      <c r="L30" s="9"/>
+      <c r="M30" s="9"/>
+      <c r="N30" s="9"/>
+      <c r="O30" s="9"/>
+      <c r="P30" s="9"/>
+      <c r="Q30" s="9"/>
+      <c r="R30" s="9"/>
+      <c r="S30" s="9"/>
+      <c r="T30" s="9"/>
+      <c r="U30" s="9"/>
+      <c r="V30" s="9"/>
+      <c r="W30" s="9"/>
+      <c r="X30" s="9"/>
+      <c r="Y30" s="9"/>
+      <c r="Z30" s="9"/>
+      <c r="AA30" s="9"/>
+      <c r="AB30" s="9"/>
+      <c r="AC30" s="9"/>
+      <c r="AD30" s="9"/>
+      <c r="AE30" s="9"/>
+      <c r="AF30" s="9"/>
+      <c r="AG30" s="9"/>
+      <c r="AH30" s="9"/>
+      <c r="AI30" s="9"/>
+      <c r="AJ30" s="9"/>
+      <c r="AK30" s="9"/>
+      <c r="AL30" s="9"/>
+      <c r="AM30" s="9"/>
+      <c r="AN30" s="9"/>
+      <c r="AO30" s="9"/>
+      <c r="AP30" s="9"/>
+      <c r="AQ30" s="9"/>
+      <c r="AR30" s="9"/>
+      <c r="AS30" s="9"/>
+      <c r="AT30" s="9"/>
+      <c r="AU30" s="9"/>
+      <c r="AV30" s="9"/>
+      <c r="AW30" s="9"/>
+      <c r="AX30" s="9"/>
+      <c r="AY30" s="9"/>
     </row>
     <row r="31" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="12"/>
-      <c r="C31" s="12"/>
-      <c r="D31" s="12"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="12"/>
-      <c r="H31" s="12"/>
-      <c r="I31" s="12"/>
-      <c r="J31" s="12"/>
-      <c r="K31" s="12"/>
-      <c r="L31" s="12"/>
-      <c r="M31" s="12"/>
-      <c r="N31" s="12"/>
-      <c r="O31" s="12"/>
-      <c r="P31" s="12"/>
-      <c r="Q31" s="12"/>
-      <c r="R31" s="12"/>
-      <c r="S31" s="12"/>
-      <c r="T31" s="12"/>
-      <c r="U31" s="12"/>
-      <c r="V31" s="12"/>
-      <c r="W31" s="12"/>
-      <c r="X31" s="12"/>
-      <c r="Y31" s="12"/>
-      <c r="Z31" s="12"/>
-      <c r="AA31" s="12"/>
-      <c r="AB31" s="12"/>
-      <c r="AC31" s="12"/>
-      <c r="AD31" s="12"/>
-      <c r="AE31" s="12"/>
-      <c r="AF31" s="12"/>
-      <c r="AG31" s="12"/>
-      <c r="AH31" s="12"/>
-      <c r="AI31" s="12"/>
-      <c r="AJ31" s="12"/>
-      <c r="AK31" s="12"/>
-      <c r="AL31" s="12"/>
-      <c r="AM31" s="12"/>
-      <c r="AN31" s="12"/>
-      <c r="AO31" s="12"/>
-      <c r="AP31" s="12"/>
-      <c r="AQ31" s="12"/>
-      <c r="AR31" s="12"/>
-      <c r="AS31" s="12"/>
-      <c r="AT31" s="12"/>
-      <c r="AU31" s="12"/>
-      <c r="AV31" s="12"/>
-      <c r="AW31" s="12"/>
-      <c r="AX31" s="12"/>
-      <c r="AY31" s="12"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="9"/>
+      <c r="H31" s="9"/>
+      <c r="I31" s="9"/>
+      <c r="J31" s="9"/>
+      <c r="K31" s="9"/>
+      <c r="L31" s="9"/>
+      <c r="M31" s="9"/>
+      <c r="N31" s="9"/>
+      <c r="O31" s="9"/>
+      <c r="P31" s="9"/>
+      <c r="Q31" s="9"/>
+      <c r="R31" s="9"/>
+      <c r="S31" s="9"/>
+      <c r="T31" s="9"/>
+      <c r="U31" s="9"/>
+      <c r="V31" s="9"/>
+      <c r="W31" s="9"/>
+      <c r="X31" s="9"/>
+      <c r="Y31" s="9"/>
+      <c r="Z31" s="9"/>
+      <c r="AA31" s="9"/>
+      <c r="AB31" s="9"/>
+      <c r="AC31" s="9"/>
+      <c r="AD31" s="9"/>
+      <c r="AE31" s="9"/>
+      <c r="AF31" s="9"/>
+      <c r="AG31" s="9"/>
+      <c r="AH31" s="9"/>
+      <c r="AI31" s="9"/>
+      <c r="AJ31" s="9"/>
+      <c r="AK31" s="9"/>
+      <c r="AL31" s="9"/>
+      <c r="AM31" s="9"/>
+      <c r="AN31" s="9"/>
+      <c r="AO31" s="9"/>
+      <c r="AP31" s="9"/>
+      <c r="AQ31" s="9"/>
+      <c r="AR31" s="9"/>
+      <c r="AS31" s="9"/>
+      <c r="AT31" s="9"/>
+      <c r="AU31" s="9"/>
+      <c r="AV31" s="9"/>
+      <c r="AW31" s="9"/>
+      <c r="AX31" s="9"/>
+      <c r="AY31" s="9"/>
     </row>
     <row r="32" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="12"/>
-      <c r="C32" s="12"/>
-      <c r="D32" s="12"/>
-      <c r="E32" s="12"/>
-      <c r="F32" s="12"/>
-      <c r="G32" s="12"/>
-      <c r="H32" s="12"/>
-      <c r="I32" s="12"/>
-      <c r="J32" s="12"/>
-      <c r="K32" s="12"/>
-      <c r="L32" s="12"/>
-      <c r="M32" s="12"/>
-      <c r="N32" s="12"/>
-      <c r="O32" s="12"/>
-      <c r="P32" s="12"/>
-      <c r="Q32" s="12"/>
-      <c r="R32" s="12"/>
-      <c r="S32" s="12"/>
-      <c r="T32" s="12"/>
-      <c r="U32" s="12"/>
-      <c r="V32" s="12"/>
-      <c r="W32" s="12"/>
-      <c r="X32" s="12"/>
-      <c r="Y32" s="12"/>
-      <c r="Z32" s="12"/>
-      <c r="AA32" s="12"/>
-      <c r="AB32" s="12"/>
-      <c r="AC32" s="12"/>
-      <c r="AD32" s="12"/>
-      <c r="AE32" s="12"/>
-      <c r="AF32" s="12"/>
-      <c r="AG32" s="12"/>
-      <c r="AH32" s="12"/>
-      <c r="AI32" s="12"/>
-      <c r="AJ32" s="12"/>
-      <c r="AK32" s="12"/>
-      <c r="AL32" s="12"/>
-      <c r="AM32" s="12"/>
-      <c r="AN32" s="12"/>
-      <c r="AO32" s="12"/>
-      <c r="AP32" s="12"/>
-      <c r="AQ32" s="12"/>
-      <c r="AR32" s="12"/>
-      <c r="AS32" s="12"/>
-      <c r="AT32" s="12"/>
-      <c r="AU32" s="12"/>
-      <c r="AV32" s="12"/>
-      <c r="AW32" s="12"/>
-      <c r="AX32" s="12"/>
-      <c r="AY32" s="12"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="9"/>
+      <c r="G32" s="9"/>
+      <c r="H32" s="9"/>
+      <c r="I32" s="9"/>
+      <c r="J32" s="9"/>
+      <c r="K32" s="9"/>
+      <c r="L32" s="9"/>
+      <c r="M32" s="9"/>
+      <c r="N32" s="9"/>
+      <c r="O32" s="9"/>
+      <c r="P32" s="9"/>
+      <c r="Q32" s="9"/>
+      <c r="R32" s="9"/>
+      <c r="S32" s="9"/>
+      <c r="T32" s="9"/>
+      <c r="U32" s="9"/>
+      <c r="V32" s="9"/>
+      <c r="W32" s="9"/>
+      <c r="X32" s="9"/>
+      <c r="Y32" s="9"/>
+      <c r="Z32" s="9"/>
+      <c r="AA32" s="9"/>
+      <c r="AB32" s="9"/>
+      <c r="AC32" s="9"/>
+      <c r="AD32" s="9"/>
+      <c r="AE32" s="9"/>
+      <c r="AF32" s="9"/>
+      <c r="AG32" s="9"/>
+      <c r="AH32" s="9"/>
+      <c r="AI32" s="9"/>
+      <c r="AJ32" s="9"/>
+      <c r="AK32" s="9"/>
+      <c r="AL32" s="9"/>
+      <c r="AM32" s="9"/>
+      <c r="AN32" s="9"/>
+      <c r="AO32" s="9"/>
+      <c r="AP32" s="9"/>
+      <c r="AQ32" s="9"/>
+      <c r="AR32" s="9"/>
+      <c r="AS32" s="9"/>
+      <c r="AT32" s="9"/>
+      <c r="AU32" s="9"/>
+      <c r="AV32" s="9"/>
+      <c r="AW32" s="9"/>
+      <c r="AX32" s="9"/>
+      <c r="AY32" s="9"/>
     </row>
     <row r="33" spans="2:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B33" s="12"/>
-      <c r="C33" s="12"/>
-      <c r="D33" s="12"/>
-      <c r="E33" s="12"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="12"/>
-      <c r="H33" s="12"/>
-      <c r="I33" s="12"/>
-      <c r="J33" s="12"/>
-      <c r="K33" s="12"/>
-      <c r="L33" s="12"/>
-      <c r="M33" s="12"/>
-      <c r="N33" s="12"/>
-      <c r="O33" s="12"/>
-      <c r="P33" s="12"/>
-      <c r="Q33" s="12"/>
-      <c r="R33" s="12"/>
-      <c r="S33" s="12"/>
-      <c r="T33" s="12"/>
-      <c r="U33" s="12"/>
-      <c r="V33" s="12"/>
-      <c r="W33" s="12"/>
-      <c r="X33" s="12"/>
-      <c r="Y33" s="12"/>
-      <c r="Z33" s="12"/>
-      <c r="AA33" s="12"/>
-      <c r="AB33" s="12"/>
-      <c r="AC33" s="12"/>
-      <c r="AD33" s="12"/>
-      <c r="AE33" s="12"/>
-      <c r="AF33" s="12"/>
-      <c r="AG33" s="12"/>
-      <c r="AH33" s="12"/>
-      <c r="AI33" s="12"/>
-      <c r="AJ33" s="12"/>
-      <c r="AK33" s="12"/>
-      <c r="AL33" s="12"/>
-      <c r="AM33" s="12"/>
-      <c r="AN33" s="12"/>
-      <c r="AO33" s="12"/>
-      <c r="AP33" s="12"/>
-      <c r="AQ33" s="12"/>
-      <c r="AR33" s="12"/>
-      <c r="AS33" s="12"/>
-      <c r="AT33" s="12"/>
-      <c r="AU33" s="12"/>
-      <c r="AV33" s="12"/>
-      <c r="AW33" s="12"/>
-      <c r="AX33" s="12"/>
-      <c r="AY33" s="12"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="9"/>
+      <c r="G33" s="9"/>
+      <c r="H33" s="9"/>
+      <c r="I33" s="9"/>
+      <c r="J33" s="9"/>
+      <c r="K33" s="9"/>
+      <c r="L33" s="9"/>
+      <c r="M33" s="9"/>
+      <c r="N33" s="9"/>
+      <c r="O33" s="9"/>
+      <c r="P33" s="9"/>
+      <c r="Q33" s="9"/>
+      <c r="R33" s="9"/>
+      <c r="S33" s="9"/>
+      <c r="T33" s="9"/>
+      <c r="U33" s="9"/>
+      <c r="V33" s="9"/>
+      <c r="W33" s="9"/>
+      <c r="X33" s="9"/>
+      <c r="Y33" s="9"/>
+      <c r="Z33" s="9"/>
+      <c r="AA33" s="9"/>
+      <c r="AB33" s="9"/>
+      <c r="AC33" s="9"/>
+      <c r="AD33" s="9"/>
+      <c r="AE33" s="9"/>
+      <c r="AF33" s="9"/>
+      <c r="AG33" s="9"/>
+      <c r="AH33" s="9"/>
+      <c r="AI33" s="9"/>
+      <c r="AJ33" s="9"/>
+      <c r="AK33" s="9"/>
+      <c r="AL33" s="9"/>
+      <c r="AM33" s="9"/>
+      <c r="AN33" s="9"/>
+      <c r="AO33" s="9"/>
+      <c r="AP33" s="9"/>
+      <c r="AQ33" s="9"/>
+      <c r="AR33" s="9"/>
+      <c r="AS33" s="9"/>
+      <c r="AT33" s="9"/>
+      <c r="AU33" s="9"/>
+      <c r="AV33" s="9"/>
+      <c r="AW33" s="9"/>
+      <c r="AX33" s="9"/>
+      <c r="AY33" s="9"/>
     </row>
     <row r="34" spans="2:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B34" s="12"/>
-      <c r="C34" s="12"/>
-      <c r="D34" s="12"/>
-      <c r="E34" s="12"/>
-      <c r="F34" s="12"/>
-      <c r="G34" s="12"/>
-      <c r="H34" s="12"/>
-      <c r="I34" s="12"/>
-      <c r="J34" s="12"/>
-      <c r="K34" s="12"/>
-      <c r="L34" s="12"/>
-      <c r="M34" s="12"/>
-      <c r="N34" s="12"/>
-      <c r="O34" s="12"/>
-      <c r="P34" s="12"/>
-      <c r="Q34" s="12"/>
-      <c r="R34" s="12"/>
-      <c r="S34" s="12"/>
-      <c r="T34" s="12"/>
-      <c r="U34" s="12"/>
-      <c r="V34" s="12"/>
-      <c r="W34" s="12"/>
-      <c r="X34" s="12"/>
-      <c r="Y34" s="12"/>
-      <c r="Z34" s="12"/>
-      <c r="AA34" s="12"/>
-      <c r="AB34" s="12"/>
-      <c r="AC34" s="12"/>
-      <c r="AD34" s="12"/>
-      <c r="AE34" s="12"/>
-      <c r="AF34" s="12"/>
-      <c r="AG34" s="12"/>
-      <c r="AH34" s="12"/>
-      <c r="AI34" s="12"/>
-      <c r="AJ34" s="12"/>
-      <c r="AK34" s="12"/>
-      <c r="AL34" s="12"/>
-      <c r="AM34" s="12"/>
-      <c r="AN34" s="12"/>
-      <c r="AO34" s="12"/>
-      <c r="AP34" s="12"/>
-      <c r="AQ34" s="12"/>
-      <c r="AR34" s="12"/>
-      <c r="AS34" s="12"/>
-      <c r="AT34" s="12"/>
-      <c r="AU34" s="12"/>
-      <c r="AV34" s="12"/>
-      <c r="AW34" s="12"/>
-      <c r="AX34" s="12"/>
-      <c r="AY34" s="12"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="9"/>
+      <c r="H34" s="9"/>
+      <c r="I34" s="9"/>
+      <c r="J34" s="9"/>
+      <c r="K34" s="9"/>
+      <c r="L34" s="9"/>
+      <c r="M34" s="9"/>
+      <c r="N34" s="9"/>
+      <c r="O34" s="9"/>
+      <c r="P34" s="9"/>
+      <c r="Q34" s="9"/>
+      <c r="R34" s="9"/>
+      <c r="S34" s="9"/>
+      <c r="T34" s="9"/>
+      <c r="U34" s="9"/>
+      <c r="V34" s="9"/>
+      <c r="W34" s="9"/>
+      <c r="X34" s="9"/>
+      <c r="Y34" s="9"/>
+      <c r="Z34" s="9"/>
+      <c r="AA34" s="9"/>
+      <c r="AB34" s="9"/>
+      <c r="AC34" s="9"/>
+      <c r="AD34" s="9"/>
+      <c r="AE34" s="9"/>
+      <c r="AF34" s="9"/>
+      <c r="AG34" s="9"/>
+      <c r="AH34" s="9"/>
+      <c r="AI34" s="9"/>
+      <c r="AJ34" s="9"/>
+      <c r="AK34" s="9"/>
+      <c r="AL34" s="9"/>
+      <c r="AM34" s="9"/>
+      <c r="AN34" s="9"/>
+      <c r="AO34" s="9"/>
+      <c r="AP34" s="9"/>
+      <c r="AQ34" s="9"/>
+      <c r="AR34" s="9"/>
+      <c r="AS34" s="9"/>
+      <c r="AT34" s="9"/>
+      <c r="AU34" s="9"/>
+      <c r="AV34" s="9"/>
+      <c r="AW34" s="9"/>
+      <c r="AX34" s="9"/>
+      <c r="AY34" s="9"/>
     </row>
     <row r="35" spans="2:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B35" s="12"/>
-      <c r="C35" s="12"/>
-      <c r="D35" s="12"/>
-      <c r="E35" s="12"/>
-      <c r="F35" s="12"/>
-      <c r="G35" s="12"/>
-      <c r="H35" s="12"/>
-      <c r="I35" s="12"/>
-      <c r="J35" s="12"/>
-      <c r="K35" s="12"/>
-      <c r="L35" s="12"/>
-      <c r="M35" s="12"/>
-      <c r="N35" s="12"/>
-      <c r="O35" s="12"/>
-      <c r="P35" s="12"/>
-      <c r="Q35" s="12"/>
-      <c r="R35" s="12"/>
-      <c r="S35" s="12"/>
-      <c r="T35" s="12"/>
-      <c r="U35" s="12"/>
-      <c r="V35" s="12"/>
-      <c r="W35" s="12"/>
-      <c r="X35" s="12"/>
-      <c r="Y35" s="12"/>
-      <c r="Z35" s="12"/>
-      <c r="AA35" s="12"/>
-      <c r="AB35" s="12"/>
-      <c r="AC35" s="12"/>
-      <c r="AD35" s="12"/>
-      <c r="AE35" s="12"/>
-      <c r="AF35" s="12"/>
-      <c r="AG35" s="12"/>
-      <c r="AH35" s="12"/>
-      <c r="AI35" s="12"/>
-      <c r="AJ35" s="12"/>
-      <c r="AK35" s="12"/>
-      <c r="AL35" s="12"/>
-      <c r="AM35" s="12"/>
-      <c r="AN35" s="12"/>
-      <c r="AO35" s="12"/>
-      <c r="AP35" s="12"/>
-      <c r="AQ35" s="12"/>
-      <c r="AR35" s="12"/>
-      <c r="AS35" s="12"/>
-      <c r="AT35" s="12"/>
-      <c r="AU35" s="12"/>
-      <c r="AV35" s="12"/>
-      <c r="AW35" s="12"/>
-      <c r="AX35" s="12"/>
-      <c r="AY35" s="12"/>
+      <c r="B35" s="9"/>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="9"/>
+      <c r="F35" s="9"/>
+      <c r="G35" s="9"/>
+      <c r="H35" s="9"/>
+      <c r="I35" s="9"/>
+      <c r="J35" s="9"/>
+      <c r="K35" s="9"/>
+      <c r="L35" s="9"/>
+      <c r="M35" s="9"/>
+      <c r="N35" s="9"/>
+      <c r="O35" s="9"/>
+      <c r="P35" s="9"/>
+      <c r="Q35" s="9"/>
+      <c r="R35" s="9"/>
+      <c r="S35" s="9"/>
+      <c r="T35" s="9"/>
+      <c r="U35" s="9"/>
+      <c r="V35" s="9"/>
+      <c r="W35" s="9"/>
+      <c r="X35" s="9"/>
+      <c r="Y35" s="9"/>
+      <c r="Z35" s="9"/>
+      <c r="AA35" s="9"/>
+      <c r="AB35" s="9"/>
+      <c r="AC35" s="9"/>
+      <c r="AD35" s="9"/>
+      <c r="AE35" s="9"/>
+      <c r="AF35" s="9"/>
+      <c r="AG35" s="9"/>
+      <c r="AH35" s="9"/>
+      <c r="AI35" s="9"/>
+      <c r="AJ35" s="9"/>
+      <c r="AK35" s="9"/>
+      <c r="AL35" s="9"/>
+      <c r="AM35" s="9"/>
+      <c r="AN35" s="9"/>
+      <c r="AO35" s="9"/>
+      <c r="AP35" s="9"/>
+      <c r="AQ35" s="9"/>
+      <c r="AR35" s="9"/>
+      <c r="AS35" s="9"/>
+      <c r="AT35" s="9"/>
+      <c r="AU35" s="9"/>
+      <c r="AV35" s="9"/>
+      <c r="AW35" s="9"/>
+      <c r="AX35" s="9"/>
+      <c r="AY35" s="9"/>
     </row>
     <row r="36" spans="2:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B36" s="12"/>
-      <c r="C36" s="12"/>
-      <c r="D36" s="12"/>
-      <c r="E36" s="12"/>
-      <c r="F36" s="12"/>
-      <c r="G36" s="12"/>
-      <c r="H36" s="12"/>
-      <c r="I36" s="12"/>
-      <c r="J36" s="12"/>
-      <c r="K36" s="12"/>
-      <c r="L36" s="12"/>
-      <c r="M36" s="12"/>
-      <c r="N36" s="12"/>
-      <c r="O36" s="12"/>
-      <c r="P36" s="12"/>
-      <c r="Q36" s="12"/>
-      <c r="R36" s="12"/>
-      <c r="S36" s="12"/>
-      <c r="T36" s="12"/>
-      <c r="U36" s="12"/>
-      <c r="V36" s="12"/>
-      <c r="W36" s="12"/>
-      <c r="X36" s="12"/>
-      <c r="Y36" s="12"/>
-      <c r="Z36" s="12"/>
-      <c r="AA36" s="12"/>
-      <c r="AB36" s="12"/>
-      <c r="AC36" s="12"/>
-      <c r="AD36" s="12"/>
-      <c r="AE36" s="12"/>
-      <c r="AF36" s="12"/>
-      <c r="AG36" s="12"/>
-      <c r="AH36" s="12"/>
-      <c r="AI36" s="12"/>
-      <c r="AJ36" s="12"/>
-      <c r="AK36" s="12"/>
-      <c r="AL36" s="12"/>
-      <c r="AM36" s="12"/>
-      <c r="AN36" s="12"/>
-      <c r="AO36" s="12"/>
-      <c r="AP36" s="12"/>
-      <c r="AQ36" s="12"/>
-      <c r="AR36" s="12"/>
-      <c r="AS36" s="12"/>
-      <c r="AT36" s="12"/>
-      <c r="AU36" s="12"/>
-      <c r="AV36" s="12"/>
-      <c r="AW36" s="12"/>
-      <c r="AX36" s="12"/>
-      <c r="AY36" s="12"/>
+      <c r="B36" s="9"/>
+      <c r="C36" s="9"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="9"/>
+      <c r="F36" s="9"/>
+      <c r="G36" s="9"/>
+      <c r="H36" s="9"/>
+      <c r="I36" s="9"/>
+      <c r="J36" s="9"/>
+      <c r="K36" s="9"/>
+      <c r="L36" s="9"/>
+      <c r="M36" s="9"/>
+      <c r="N36" s="9"/>
+      <c r="O36" s="9"/>
+      <c r="P36" s="9"/>
+      <c r="Q36" s="9"/>
+      <c r="R36" s="9"/>
+      <c r="S36" s="9"/>
+      <c r="T36" s="9"/>
+      <c r="U36" s="9"/>
+      <c r="V36" s="9"/>
+      <c r="W36" s="9"/>
+      <c r="X36" s="9"/>
+      <c r="Y36" s="9"/>
+      <c r="Z36" s="9"/>
+      <c r="AA36" s="9"/>
+      <c r="AB36" s="9"/>
+      <c r="AC36" s="9"/>
+      <c r="AD36" s="9"/>
+      <c r="AE36" s="9"/>
+      <c r="AF36" s="9"/>
+      <c r="AG36" s="9"/>
+      <c r="AH36" s="9"/>
+      <c r="AI36" s="9"/>
+      <c r="AJ36" s="9"/>
+      <c r="AK36" s="9"/>
+      <c r="AL36" s="9"/>
+      <c r="AM36" s="9"/>
+      <c r="AN36" s="9"/>
+      <c r="AO36" s="9"/>
+      <c r="AP36" s="9"/>
+      <c r="AQ36" s="9"/>
+      <c r="AR36" s="9"/>
+      <c r="AS36" s="9"/>
+      <c r="AT36" s="9"/>
+      <c r="AU36" s="9"/>
+      <c r="AV36" s="9"/>
+      <c r="AW36" s="9"/>
+      <c r="AX36" s="9"/>
+      <c r="AY36" s="9"/>
     </row>
     <row r="37" spans="2:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B37" s="12"/>
-      <c r="C37" s="12"/>
-      <c r="D37" s="12"/>
-      <c r="E37" s="12"/>
-      <c r="F37" s="12"/>
-      <c r="G37" s="12"/>
-      <c r="H37" s="12"/>
-      <c r="I37" s="12"/>
-      <c r="J37" s="12"/>
-      <c r="K37" s="12"/>
-      <c r="L37" s="12"/>
-      <c r="M37" s="12"/>
-      <c r="N37" s="12"/>
-      <c r="O37" s="12"/>
-      <c r="P37" s="12"/>
-      <c r="Q37" s="12"/>
-      <c r="R37" s="12"/>
-      <c r="S37" s="12"/>
-      <c r="T37" s="12"/>
-      <c r="U37" s="12"/>
-      <c r="V37" s="12"/>
-      <c r="W37" s="12"/>
-      <c r="X37" s="12"/>
-      <c r="Y37" s="12"/>
-      <c r="Z37" s="12"/>
-      <c r="AA37" s="12"/>
-      <c r="AB37" s="12"/>
-      <c r="AC37" s="12"/>
-      <c r="AD37" s="12"/>
-      <c r="AE37" s="12"/>
-      <c r="AF37" s="12"/>
-      <c r="AG37" s="12"/>
-      <c r="AH37" s="12"/>
-      <c r="AI37" s="12"/>
-      <c r="AJ37" s="12"/>
-      <c r="AK37" s="12"/>
-      <c r="AL37" s="12"/>
-      <c r="AM37" s="12"/>
-      <c r="AN37" s="12"/>
-      <c r="AO37" s="12"/>
-      <c r="AP37" s="12"/>
-      <c r="AQ37" s="12"/>
-      <c r="AR37" s="12"/>
-      <c r="AS37" s="12"/>
-      <c r="AT37" s="12"/>
-      <c r="AU37" s="12"/>
-      <c r="AV37" s="12"/>
-      <c r="AW37" s="12"/>
-      <c r="AX37" s="12"/>
-      <c r="AY37" s="12"/>
+      <c r="B37" s="9"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="9"/>
+      <c r="H37" s="9"/>
+      <c r="I37" s="9"/>
+      <c r="J37" s="9"/>
+      <c r="K37" s="9"/>
+      <c r="L37" s="9"/>
+      <c r="M37" s="9"/>
+      <c r="N37" s="9"/>
+      <c r="O37" s="9"/>
+      <c r="P37" s="9"/>
+      <c r="Q37" s="9"/>
+      <c r="R37" s="9"/>
+      <c r="S37" s="9"/>
+      <c r="T37" s="9"/>
+      <c r="U37" s="9"/>
+      <c r="V37" s="9"/>
+      <c r="W37" s="9"/>
+      <c r="X37" s="9"/>
+      <c r="Y37" s="9"/>
+      <c r="Z37" s="9"/>
+      <c r="AA37" s="9"/>
+      <c r="AB37" s="9"/>
+      <c r="AC37" s="9"/>
+      <c r="AD37" s="9"/>
+      <c r="AE37" s="9"/>
+      <c r="AF37" s="9"/>
+      <c r="AG37" s="9"/>
+      <c r="AH37" s="9"/>
+      <c r="AI37" s="9"/>
+      <c r="AJ37" s="9"/>
+      <c r="AK37" s="9"/>
+      <c r="AL37" s="9"/>
+      <c r="AM37" s="9"/>
+      <c r="AN37" s="9"/>
+      <c r="AO37" s="9"/>
+      <c r="AP37" s="9"/>
+      <c r="AQ37" s="9"/>
+      <c r="AR37" s="9"/>
+      <c r="AS37" s="9"/>
+      <c r="AT37" s="9"/>
+      <c r="AU37" s="9"/>
+      <c r="AV37" s="9"/>
+      <c r="AW37" s="9"/>
+      <c r="AX37" s="9"/>
+      <c r="AY37" s="9"/>
     </row>
     <row r="38" spans="2:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B38" s="12"/>
-      <c r="C38" s="12"/>
-      <c r="D38" s="12"/>
-      <c r="E38" s="12"/>
-      <c r="F38" s="12"/>
-      <c r="G38" s="12"/>
-      <c r="H38" s="12"/>
-      <c r="I38" s="12"/>
-      <c r="J38" s="12"/>
-      <c r="K38" s="12"/>
-      <c r="L38" s="12"/>
-      <c r="M38" s="12"/>
-      <c r="N38" s="12"/>
-      <c r="O38" s="12"/>
-      <c r="P38" s="12"/>
-      <c r="Q38" s="12"/>
-      <c r="R38" s="12"/>
-      <c r="S38" s="12"/>
-      <c r="T38" s="12"/>
-      <c r="U38" s="12"/>
-      <c r="V38" s="12"/>
-      <c r="W38" s="12"/>
-      <c r="X38" s="12"/>
-      <c r="Y38" s="12"/>
-      <c r="Z38" s="12"/>
-      <c r="AA38" s="12"/>
-      <c r="AB38" s="12"/>
-      <c r="AC38" s="12"/>
-      <c r="AD38" s="12"/>
-      <c r="AE38" s="12"/>
-      <c r="AF38" s="12"/>
-      <c r="AG38" s="12"/>
-      <c r="AH38" s="12"/>
-      <c r="AI38" s="12"/>
-      <c r="AJ38" s="12"/>
-      <c r="AK38" s="12"/>
-      <c r="AL38" s="12"/>
-      <c r="AM38" s="12"/>
-      <c r="AN38" s="12"/>
-      <c r="AO38" s="12"/>
-      <c r="AP38" s="12"/>
-      <c r="AQ38" s="12"/>
-      <c r="AR38" s="12"/>
-      <c r="AS38" s="12"/>
-      <c r="AT38" s="12"/>
-      <c r="AU38" s="12"/>
-      <c r="AV38" s="12"/>
-      <c r="AW38" s="12"/>
-      <c r="AX38" s="12"/>
-      <c r="AY38" s="12"/>
+      <c r="B38" s="9"/>
+      <c r="C38" s="9"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="9"/>
+      <c r="F38" s="9"/>
+      <c r="G38" s="9"/>
+      <c r="H38" s="9"/>
+      <c r="I38" s="9"/>
+      <c r="J38" s="9"/>
+      <c r="K38" s="9"/>
+      <c r="L38" s="9"/>
+      <c r="M38" s="9"/>
+      <c r="N38" s="9"/>
+      <c r="O38" s="9"/>
+      <c r="P38" s="9"/>
+      <c r="Q38" s="9"/>
+      <c r="R38" s="9"/>
+      <c r="S38" s="9"/>
+      <c r="T38" s="9"/>
+      <c r="U38" s="9"/>
+      <c r="V38" s="9"/>
+      <c r="W38" s="9"/>
+      <c r="X38" s="9"/>
+      <c r="Y38" s="9"/>
+      <c r="Z38" s="9"/>
+      <c r="AA38" s="9"/>
+      <c r="AB38" s="9"/>
+      <c r="AC38" s="9"/>
+      <c r="AD38" s="9"/>
+      <c r="AE38" s="9"/>
+      <c r="AF38" s="9"/>
+      <c r="AG38" s="9"/>
+      <c r="AH38" s="9"/>
+      <c r="AI38" s="9"/>
+      <c r="AJ38" s="9"/>
+      <c r="AK38" s="9"/>
+      <c r="AL38" s="9"/>
+      <c r="AM38" s="9"/>
+      <c r="AN38" s="9"/>
+      <c r="AO38" s="9"/>
+      <c r="AP38" s="9"/>
+      <c r="AQ38" s="9"/>
+      <c r="AR38" s="9"/>
+      <c r="AS38" s="9"/>
+      <c r="AT38" s="9"/>
+      <c r="AU38" s="9"/>
+      <c r="AV38" s="9"/>
+      <c r="AW38" s="9"/>
+      <c r="AX38" s="9"/>
+      <c r="AY38" s="9"/>
     </row>
     <row r="39" spans="2:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="12"/>
-      <c r="C39" s="12"/>
-      <c r="D39" s="12"/>
-      <c r="E39" s="12"/>
-      <c r="F39" s="12"/>
-      <c r="G39" s="12"/>
-      <c r="H39" s="12"/>
-      <c r="I39" s="12"/>
-      <c r="J39" s="12"/>
-      <c r="K39" s="12"/>
-      <c r="L39" s="12"/>
-      <c r="M39" s="12"/>
-      <c r="N39" s="12"/>
-      <c r="O39" s="12"/>
-      <c r="P39" s="12"/>
-      <c r="Q39" s="12"/>
-      <c r="R39" s="12"/>
-      <c r="S39" s="12"/>
-      <c r="T39" s="12"/>
-      <c r="U39" s="12"/>
-      <c r="V39" s="12"/>
-      <c r="W39" s="12"/>
-      <c r="X39" s="12"/>
-      <c r="Y39" s="12"/>
-      <c r="Z39" s="12"/>
-      <c r="AA39" s="12"/>
-      <c r="AB39" s="12"/>
-      <c r="AC39" s="12"/>
-      <c r="AD39" s="12"/>
-      <c r="AE39" s="12"/>
-      <c r="AF39" s="12"/>
-      <c r="AG39" s="12"/>
-      <c r="AH39" s="12"/>
-      <c r="AI39" s="12"/>
-      <c r="AJ39" s="12"/>
-      <c r="AK39" s="12"/>
-      <c r="AL39" s="12"/>
-      <c r="AM39" s="12"/>
-      <c r="AN39" s="12"/>
-      <c r="AO39" s="12"/>
-      <c r="AP39" s="12"/>
-      <c r="AQ39" s="12"/>
-      <c r="AR39" s="12"/>
-      <c r="AS39" s="12"/>
-      <c r="AT39" s="12"/>
-      <c r="AU39" s="12"/>
-      <c r="AV39" s="12"/>
-      <c r="AW39" s="12"/>
-      <c r="AX39" s="12"/>
-      <c r="AY39" s="12"/>
+      <c r="B39" s="9"/>
+      <c r="C39" s="9"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="9"/>
+      <c r="F39" s="9"/>
+      <c r="G39" s="9"/>
+      <c r="H39" s="9"/>
+      <c r="I39" s="9"/>
+      <c r="J39" s="9"/>
+      <c r="K39" s="9"/>
+      <c r="L39" s="9"/>
+      <c r="M39" s="9"/>
+      <c r="N39" s="9"/>
+      <c r="O39" s="9"/>
+      <c r="P39" s="9"/>
+      <c r="Q39" s="9"/>
+      <c r="R39" s="9"/>
+      <c r="S39" s="9"/>
+      <c r="T39" s="9"/>
+      <c r="U39" s="9"/>
+      <c r="V39" s="9"/>
+      <c r="W39" s="9"/>
+      <c r="X39" s="9"/>
+      <c r="Y39" s="9"/>
+      <c r="Z39" s="9"/>
+      <c r="AA39" s="9"/>
+      <c r="AB39" s="9"/>
+      <c r="AC39" s="9"/>
+      <c r="AD39" s="9"/>
+      <c r="AE39" s="9"/>
+      <c r="AF39" s="9"/>
+      <c r="AG39" s="9"/>
+      <c r="AH39" s="9"/>
+      <c r="AI39" s="9"/>
+      <c r="AJ39" s="9"/>
+      <c r="AK39" s="9"/>
+      <c r="AL39" s="9"/>
+      <c r="AM39" s="9"/>
+      <c r="AN39" s="9"/>
+      <c r="AO39" s="9"/>
+      <c r="AP39" s="9"/>
+      <c r="AQ39" s="9"/>
+      <c r="AR39" s="9"/>
+      <c r="AS39" s="9"/>
+      <c r="AT39" s="9"/>
+      <c r="AU39" s="9"/>
+      <c r="AV39" s="9"/>
+      <c r="AW39" s="9"/>
+      <c r="AX39" s="9"/>
+      <c r="AY39" s="9"/>
     </row>
     <row r="40" spans="2:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B40" s="12"/>
-      <c r="C40" s="12"/>
-      <c r="D40" s="12"/>
-      <c r="E40" s="12"/>
-      <c r="F40" s="12"/>
-      <c r="G40" s="12"/>
-      <c r="H40" s="12"/>
-      <c r="I40" s="12"/>
-      <c r="J40" s="12"/>
-      <c r="K40" s="12"/>
-      <c r="L40" s="12"/>
-      <c r="M40" s="12"/>
-      <c r="N40" s="12"/>
-      <c r="O40" s="12"/>
-      <c r="P40" s="12"/>
-      <c r="Q40" s="12"/>
-      <c r="R40" s="12"/>
-      <c r="S40" s="12"/>
-      <c r="T40" s="12"/>
-      <c r="U40" s="12"/>
-      <c r="V40" s="12"/>
-      <c r="W40" s="12"/>
-      <c r="X40" s="12"/>
-      <c r="Y40" s="12"/>
-      <c r="Z40" s="12"/>
-      <c r="AA40" s="12"/>
-      <c r="AB40" s="12"/>
-      <c r="AC40" s="12"/>
-      <c r="AD40" s="12"/>
-      <c r="AE40" s="12"/>
-      <c r="AF40" s="12"/>
-      <c r="AG40" s="12"/>
-      <c r="AH40" s="12"/>
-      <c r="AI40" s="12"/>
-      <c r="AJ40" s="12"/>
-      <c r="AK40" s="12"/>
-      <c r="AL40" s="12"/>
-      <c r="AM40" s="12"/>
-      <c r="AN40" s="12"/>
-      <c r="AO40" s="12"/>
-      <c r="AP40" s="12"/>
-      <c r="AQ40" s="12"/>
-      <c r="AR40" s="12"/>
-      <c r="AS40" s="12"/>
-      <c r="AT40" s="12"/>
-      <c r="AU40" s="12"/>
-      <c r="AV40" s="12"/>
-      <c r="AW40" s="12"/>
-      <c r="AX40" s="12"/>
-      <c r="AY40" s="12"/>
+      <c r="B40" s="9"/>
+      <c r="C40" s="9"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="9"/>
+      <c r="F40" s="9"/>
+      <c r="G40" s="9"/>
+      <c r="H40" s="9"/>
+      <c r="I40" s="9"/>
+      <c r="J40" s="9"/>
+      <c r="K40" s="9"/>
+      <c r="L40" s="9"/>
+      <c r="M40" s="9"/>
+      <c r="N40" s="9"/>
+      <c r="O40" s="9"/>
+      <c r="P40" s="9"/>
+      <c r="Q40" s="9"/>
+      <c r="R40" s="9"/>
+      <c r="S40" s="9"/>
+      <c r="T40" s="9"/>
+      <c r="U40" s="9"/>
+      <c r="V40" s="9"/>
+      <c r="W40" s="9"/>
+      <c r="X40" s="9"/>
+      <c r="Y40" s="9"/>
+      <c r="Z40" s="9"/>
+      <c r="AA40" s="9"/>
+      <c r="AB40" s="9"/>
+      <c r="AC40" s="9"/>
+      <c r="AD40" s="9"/>
+      <c r="AE40" s="9"/>
+      <c r="AF40" s="9"/>
+      <c r="AG40" s="9"/>
+      <c r="AH40" s="9"/>
+      <c r="AI40" s="9"/>
+      <c r="AJ40" s="9"/>
+      <c r="AK40" s="9"/>
+      <c r="AL40" s="9"/>
+      <c r="AM40" s="9"/>
+      <c r="AN40" s="9"/>
+      <c r="AO40" s="9"/>
+      <c r="AP40" s="9"/>
+      <c r="AQ40" s="9"/>
+      <c r="AR40" s="9"/>
+      <c r="AS40" s="9"/>
+      <c r="AT40" s="9"/>
+      <c r="AU40" s="9"/>
+      <c r="AV40" s="9"/>
+      <c r="AW40" s="9"/>
+      <c r="AX40" s="9"/>
+      <c r="AY40" s="9"/>
     </row>
     <row r="41" spans="2:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="42" spans="2:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>

--- a/InputData/elec/MPCbS/Max Potential Capacity by Source.xlsx
+++ b/InputData/elec/MPCbS/Max Potential Capacity by Source.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/Postdoc Projects/eps-indonesia-cpl/InputData/elec/MPCbS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC11F070-45E2-CB41-BBFF-686B3D5B43A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8DE5C60-3A8F-2748-B281-7CB583C982AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21360" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="Data" sheetId="2" r:id="rId2"/>
     <sheet name="Data-Renewables" sheetId="4" r:id="rId3"/>
-    <sheet name="MPCbS" sheetId="3" r:id="rId4"/>
+    <sheet name="Indonesia Data" sheetId="5" r:id="rId4"/>
+    <sheet name="MPCbS" sheetId="3" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="68">
   <si>
     <t>MPCbS Max Potential Capacity by Source</t>
   </si>
@@ -198,6 +199,51 @@
   </si>
   <si>
     <t>https://iesr.or.id/en/pustaka/beyond-207-gigawatts-unleashing-indonesias-solar-potential/#:~:text=A%20geospatial%20assessment%20of%20Indonesia's,land%2Duse%20exclusions%20scenarios).</t>
+  </si>
+  <si>
+    <t>MPCS</t>
+  </si>
+  <si>
+    <t>1 mtoe to MWh</t>
+  </si>
+  <si>
+    <t>1 MWh to MW</t>
+  </si>
+  <si>
+    <t>Biomass (MW)</t>
+  </si>
+  <si>
+    <t>Biomass (mtoe)</t>
+  </si>
+  <si>
+    <t>over a year</t>
+  </si>
+  <si>
+    <t>https://www.eria.org/uploads/media/Research-Project-Report/2022-01-Biomass-Demand-Potential-Indonesia/Forecast-of-Biomass-Demand-Potential-in-Indonesia.pdf</t>
+  </si>
+  <si>
+    <t>https://www.reccessary.com/en/news/Indonesia-wind-power-capacity-target#:~:text=Dewi%20noted%20that%20Indonesia%20has,%2C%20accounting%20for%20about%2040%25.</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/2071-1050/17/3/1312</t>
+  </si>
+  <si>
+    <t>https://www.energytransitionpartnership.org/wp-content/uploads/2024/09/20240919-Roadmap-Onshore-Wind-Energy-v5.0-EN.pdf</t>
+  </si>
+  <si>
+    <t>Wind (MW) (total)</t>
+  </si>
+  <si>
+    <t>https://www.reccessary.com/en/news/Indonesia-wind-power-capacity-target</t>
+  </si>
+  <si>
+    <t>Onshore wind (MW)</t>
+  </si>
+  <si>
+    <t>Offshore wind (MW)</t>
+  </si>
+  <si>
+    <t>Geothermal (MW)</t>
   </si>
 </sst>
 </file>
@@ -296,7 +342,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -318,6 +364,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -3057,10 +3106,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27209D21-DE46-9B49-910B-40254B76F16A}">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>37</v>
       </c>
@@ -3071,7 +3120,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>13</v>
       </c>
@@ -3083,7 +3132,7 @@
         <v>95000</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>14</v>
       </c>
@@ -3095,7 +3144,7 @@
         <v>60600</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>15</v>
       </c>
@@ -3106,8 +3155,9 @@
         <f t="shared" si="0"/>
         <v>19835000</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D4" s="10"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>16</v>
       </c>
@@ -3120,7 +3170,7 @@
         <v>19835000</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>18</v>
       </c>
@@ -3132,7 +3182,7 @@
         <v>32600</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>19</v>
       </c>
@@ -3144,7 +3194,7 @@
         <v>28500</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>20</v>
       </c>
@@ -3156,7 +3206,7 @@
         <v>94200</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>35</v>
       </c>
@@ -3168,7 +3218,7 @@
         <v>32600</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>43</v>
       </c>
@@ -3182,6 +3232,129 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66ECDAB1-4503-714B-93D7-817264E3A5A9}">
+  <dimension ref="A1:B20"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="24" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="1"/>
+      <c r="B1" s="15" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B3">
+        <v>11630000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B4">
+        <f>8760</f>
+        <v>8760</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5">
+        <f>B3/B4</f>
+        <v>1327.6255707762557</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B6" s="9">
+        <f>B2*B5</f>
+        <v>50449.77168949772</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" s="12" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B10" s="9">
+        <v>154600</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" s="12" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" s="12" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B15">
+        <v>60400</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B16">
+        <v>94200</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A17" s="12" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A20" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A7" r:id="rId1" xr:uid="{93226CF1-EBC5-E042-BD1F-9F78EF29E2E7}"/>
+    <hyperlink ref="A11" r:id="rId2" location=":~:text=Dewi%20noted%20that%20Indonesia%20has,%2C%20accounting%20for%20about%2040%25." xr:uid="{7779A2B9-5497-404D-91A9-E3D5574598A4}"/>
+    <hyperlink ref="A12" r:id="rId3" xr:uid="{A74447EC-2457-6C4C-9888-8F33B56CEAE2}"/>
+    <hyperlink ref="A13" r:id="rId4" xr:uid="{DDF1EF41-E7EF-5A49-A70F-445F7DA18A1C}"/>
+    <hyperlink ref="A17" r:id="rId5" xr:uid="{1EE2E04A-034A-F64B-AE31-78F1EFAF35E2}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor rgb="FF1F497D"/>
@@ -3277,8 +3450,8 @@
         <v>18</v>
       </c>
       <c r="B9" s="9">
-        <f>'Data-Renewables'!C6</f>
-        <v>32600</v>
+        <f>'Indonesia Data'!B6</f>
+        <v>50449.77168949772</v>
       </c>
       <c r="C9" s="9"/>
     </row>
@@ -3362,7 +3535,9 @@
       </c>
       <c r="C17" s="9"/>
     </row>
-    <row r="21" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="21" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="9"/>
+    </row>
     <row r="22" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="23" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="24" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
